--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -3940,7 +3940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4044,7 +4044,7 @@
     <row r="6" ht="44" customHeight="1">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>trustpilot_avis</t>
+          <t>trustpilot_review_count</t>
         </is>
       </c>
       <c r="B6" s="21" t="n"/>
@@ -4060,320 +4060,338 @@
     <row r="7" ht="44" customHeight="1">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>marches</t>
+          <t>trustpilot_url</t>
         </is>
       </c>
       <c r="B7" s="16" t="n"/>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>futures</t>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>titre</t>
+          <t>marches</t>
         </is>
       </c>
       <c r="B8" s="16" t="n"/>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>Four routes to a funded futures account</t>
+          <t>futures</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="44" customHeight="1">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>titre</t>
         </is>
       </c>
       <c r="B9" s="16" t="n"/>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+          <t>Four routes to a funded futures account</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="44" customHeight="1">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>resume</t>
+          <t>description</t>
         </is>
       </c>
       <c r="B10" s="16" t="n"/>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="44" customHeight="1">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>presentation</t>
+          <t>resume</t>
         </is>
       </c>
       <c r="B11" s="16" t="n"/>
       <c r="C11" s="17" t="inlineStr">
         <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="44" customHeight="1">
       <c r="A12" s="15" t="inlineStr">
         <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="24" t="n">
-        <v>2024</v>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>« Founded ». Vide : « — ».</t>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>« Country ».</t>
+          <t>« Founded ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="14" ht="44" customHeight="1">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>ceo_fondateur</t>
+          <t>pays</t>
         </is>
       </c>
       <c r="B14" s="16" t="n"/>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>Christian Habibi</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
+          <t>« Country ».</t>
         </is>
       </c>
     </row>
     <row r="15" ht="44" customHeight="1">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>actifs</t>
+          <t>ceo_fondateur</t>
         </is>
       </c>
       <c r="B15" s="16" t="n"/>
       <c r="C15" s="17" t="inlineStr">
         <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+          <t>Christian Habibi</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+          <t>« CEO / Founder ». Vide : « — ».</t>
         </is>
       </c>
     </row>
     <row r="16" ht="44" customHeight="1">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>categories_actifs</t>
+          <t>actifs</t>
         </is>
       </c>
       <c r="B16" s="16" t="n"/>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>(vide — non confirmees)</t>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="44" customHeight="1">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>categories_actifs_statut</t>
+          <t>categories_actifs</t>
         </is>
       </c>
       <c r="B17" s="16" t="n"/>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>needs_confirmation</t>
+          <t>(vide — non confirmees)</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="44" customHeight="1">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>plateformes</t>
+          <t>categories_actifs_statut</t>
         </is>
       </c>
       <c r="B18" s="16" t="n"/>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+          <t>needs_confirmation</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="44" customHeight="1">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>moyens_paiement</t>
+          <t>plateformes</t>
         </is>
       </c>
       <c r="B19" s="16" t="n"/>
       <c r="C19" s="17" t="inlineStr">
         <is>
-          <t>Credit/Debit Card, Crypto</t>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="44" customHeight="1">
       <c r="A20" s="15" t="inlineStr">
         <is>
-          <t>methodes_retrait</t>
+          <t>moyens_paiement</t>
         </is>
       </c>
       <c r="B20" s="16" t="n"/>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>Crypto, Riseworks</t>
+          <t>Credit/Debit Card, Crypto</t>
         </is>
       </c>
       <c r="D20" s="18" t="inlineStr">
         <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="44" customHeight="1">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>prestataire_retrait</t>
+          <t>methodes_retrait</t>
         </is>
       </c>
       <c r="B21" s="16" t="n"/>
       <c r="C21" s="17" t="inlineStr">
         <is>
-          <t>Rise</t>
+          <t>Crypto, Riseworks</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="44" customHeight="1">
       <c r="A22" s="15" t="inlineStr">
         <is>
-          <t>levier</t>
+          <t>prestataire_retrait</t>
         </is>
       </c>
       <c r="B22" s="16" t="n"/>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>N/A (futures contracts)</t>
+          <t>Rise</t>
         </is>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="44" customHeight="1">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>levier_statut</t>
+          <t>levier</t>
         </is>
       </c>
       <c r="B23" s="16" t="n"/>
       <c r="C23" s="17" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>N/A (futures contracts)</t>
         </is>
       </c>
       <c r="D23" s="18" t="inlineStr">
         <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
         </is>
       </c>
     </row>
     <row r="24" ht="44" customHeight="1">
       <c r="A24" s="15" t="inlineStr">
         <is>
-          <t>styles_trading</t>
+          <t>levier_statut</t>
         </is>
       </c>
       <c r="B24" s="16" t="n"/>
       <c r="C24" s="17" t="inlineStr">
         <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
           <t>(vide — absent du releve)</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D25" s="18" t="inlineStr">
         <is>
           <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
         </is>
@@ -4381,10 +4399,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B17" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$A$2:$A$6</formula1>
     </dataValidation>
-    <dataValidation sqref="B23" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$A$2:$A$6</formula1>
     </dataValidation>
   </dataValidations>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -2336,7 +2336,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>trading ou payouts : la carte ou la regle s'affiche.</t>
+          <t>trading, payouts, ou live (programme de compte reel, replie sous Payouts).</t>
         </is>
       </c>
       <c r="B2" s="25" t="inlineStr">
@@ -3105,7 +3105,7 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A3:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$P$2:$P$3</formula1>
+      <formula1>=Listes!$P$2:$P$4</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$A$2:$A$6</formula1>
@@ -3896,6 +3896,11 @@
       <c r="O4" s="11" t="inlineStr">
         <is>
           <t>limite</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="inlineStr">
+        <is>
+          <t>live</t>
         </is>
       </c>
       <c r="Q4" s="11" t="inlineStr">

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -2272,7 +2272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2283,7 +2283,8 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2329,6 +2330,11 @@
       </c>
       <c r="I1" s="14" t="inlineStr">
         <is>
+          <t>essentielle</t>
+        </is>
+      </c>
+      <c r="J1" s="14" t="inlineStr">
+        <is>
           <t>source_url</t>
         </is>
       </c>
@@ -2375,6 +2381,11 @@
         </is>
       </c>
       <c r="I2" s="25" t="inlineStr">
+        <is>
+          <t>oui : affichee sur la page. Les autres restent dans le tableur sans s'afficher. Quatre par carte au plus.</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="inlineStr">
         <is>
           <t>Page officielle. Non affichee.</t>
         </is>
@@ -2409,7 +2420,12 @@
           <t>oui</t>
         </is>
       </c>
-      <c r="I3" s="17" t="n"/>
+      <c r="I3" s="17" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
+      <c r="J3" s="17" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="17" t="inlineStr">
@@ -2441,6 +2457,7 @@
       </c>
       <c r="H4" s="17" t="n"/>
       <c r="I4" s="17" t="n"/>
+      <c r="J4" s="17" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="16" t="n"/>
@@ -2452,6 +2469,7 @@
       <c r="G5" s="16" t="n"/>
       <c r="H5" s="16" t="n"/>
       <c r="I5" s="16" t="n"/>
+      <c r="J5" s="16" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="16" t="n"/>
@@ -2463,6 +2481,7 @@
       <c r="G6" s="16" t="n"/>
       <c r="H6" s="16" t="n"/>
       <c r="I6" s="16" t="n"/>
+      <c r="J6" s="16" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="16" t="n"/>
@@ -2474,6 +2493,7 @@
       <c r="G7" s="16" t="n"/>
       <c r="H7" s="16" t="n"/>
       <c r="I7" s="16" t="n"/>
+      <c r="J7" s="16" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="16" t="n"/>
@@ -2485,6 +2505,7 @@
       <c r="G8" s="16" t="n"/>
       <c r="H8" s="16" t="n"/>
       <c r="I8" s="16" t="n"/>
+      <c r="J8" s="16" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="16" t="n"/>
@@ -2496,6 +2517,7 @@
       <c r="G9" s="16" t="n"/>
       <c r="H9" s="16" t="n"/>
       <c r="I9" s="16" t="n"/>
+      <c r="J9" s="16" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="16" t="n"/>
@@ -2507,6 +2529,7 @@
       <c r="G10" s="16" t="n"/>
       <c r="H10" s="16" t="n"/>
       <c r="I10" s="16" t="n"/>
+      <c r="J10" s="16" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="16" t="n"/>
@@ -2518,6 +2541,7 @@
       <c r="G11" s="16" t="n"/>
       <c r="H11" s="16" t="n"/>
       <c r="I11" s="16" t="n"/>
+      <c r="J11" s="16" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="16" t="n"/>
@@ -2529,6 +2553,7 @@
       <c r="G12" s="16" t="n"/>
       <c r="H12" s="16" t="n"/>
       <c r="I12" s="16" t="n"/>
+      <c r="J12" s="16" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n"/>
@@ -2540,6 +2565,7 @@
       <c r="G13" s="16" t="n"/>
       <c r="H13" s="16" t="n"/>
       <c r="I13" s="16" t="n"/>
+      <c r="J13" s="16" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="16" t="n"/>
@@ -2551,6 +2577,7 @@
       <c r="G14" s="16" t="n"/>
       <c r="H14" s="16" t="n"/>
       <c r="I14" s="16" t="n"/>
+      <c r="J14" s="16" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="16" t="n"/>
@@ -2562,6 +2589,7 @@
       <c r="G15" s="16" t="n"/>
       <c r="H15" s="16" t="n"/>
       <c r="I15" s="16" t="n"/>
+      <c r="J15" s="16" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="16" t="n"/>
@@ -2573,6 +2601,7 @@
       <c r="G16" s="16" t="n"/>
       <c r="H16" s="16" t="n"/>
       <c r="I16" s="16" t="n"/>
+      <c r="J16" s="16" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="16" t="n"/>
@@ -2584,6 +2613,7 @@
       <c r="G17" s="16" t="n"/>
       <c r="H17" s="16" t="n"/>
       <c r="I17" s="16" t="n"/>
+      <c r="J17" s="16" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="16" t="n"/>
@@ -2595,6 +2625,7 @@
       <c r="G18" s="16" t="n"/>
       <c r="H18" s="16" t="n"/>
       <c r="I18" s="16" t="n"/>
+      <c r="J18" s="16" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="16" t="n"/>
@@ -2606,6 +2637,7 @@
       <c r="G19" s="16" t="n"/>
       <c r="H19" s="16" t="n"/>
       <c r="I19" s="16" t="n"/>
+      <c r="J19" s="16" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="16" t="n"/>
@@ -2617,6 +2649,7 @@
       <c r="G20" s="16" t="n"/>
       <c r="H20" s="16" t="n"/>
       <c r="I20" s="16" t="n"/>
+      <c r="J20" s="16" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="16" t="n"/>
@@ -2628,6 +2661,7 @@
       <c r="G21" s="16" t="n"/>
       <c r="H21" s="16" t="n"/>
       <c r="I21" s="16" t="n"/>
+      <c r="J21" s="16" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="16" t="n"/>
@@ -2639,6 +2673,7 @@
       <c r="G22" s="16" t="n"/>
       <c r="H22" s="16" t="n"/>
       <c r="I22" s="16" t="n"/>
+      <c r="J22" s="16" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="16" t="n"/>
@@ -2650,6 +2685,7 @@
       <c r="G23" s="16" t="n"/>
       <c r="H23" s="16" t="n"/>
       <c r="I23" s="16" t="n"/>
+      <c r="J23" s="16" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="16" t="n"/>
@@ -2661,6 +2697,7 @@
       <c r="G24" s="16" t="n"/>
       <c r="H24" s="16" t="n"/>
       <c r="I24" s="16" t="n"/>
+      <c r="J24" s="16" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="16" t="n"/>
@@ -2672,6 +2709,7 @@
       <c r="G25" s="16" t="n"/>
       <c r="H25" s="16" t="n"/>
       <c r="I25" s="16" t="n"/>
+      <c r="J25" s="16" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="16" t="n"/>
@@ -2683,6 +2721,7 @@
       <c r="G26" s="16" t="n"/>
       <c r="H26" s="16" t="n"/>
       <c r="I26" s="16" t="n"/>
+      <c r="J26" s="16" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="16" t="n"/>
@@ -2694,6 +2733,7 @@
       <c r="G27" s="16" t="n"/>
       <c r="H27" s="16" t="n"/>
       <c r="I27" s="16" t="n"/>
+      <c r="J27" s="16" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="16" t="n"/>
@@ -2705,6 +2745,7 @@
       <c r="G28" s="16" t="n"/>
       <c r="H28" s="16" t="n"/>
       <c r="I28" s="16" t="n"/>
+      <c r="J28" s="16" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="16" t="n"/>
@@ -2716,6 +2757,7 @@
       <c r="G29" s="16" t="n"/>
       <c r="H29" s="16" t="n"/>
       <c r="I29" s="16" t="n"/>
+      <c r="J29" s="16" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="16" t="n"/>
@@ -2727,6 +2769,7 @@
       <c r="G30" s="16" t="n"/>
       <c r="H30" s="16" t="n"/>
       <c r="I30" s="16" t="n"/>
+      <c r="J30" s="16" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="16" t="n"/>
@@ -2738,6 +2781,7 @@
       <c r="G31" s="16" t="n"/>
       <c r="H31" s="16" t="n"/>
       <c r="I31" s="16" t="n"/>
+      <c r="J31" s="16" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="16" t="n"/>
@@ -2749,6 +2793,7 @@
       <c r="G32" s="16" t="n"/>
       <c r="H32" s="16" t="n"/>
       <c r="I32" s="16" t="n"/>
+      <c r="J32" s="16" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="16" t="n"/>
@@ -2760,6 +2805,7 @@
       <c r="G33" s="16" t="n"/>
       <c r="H33" s="16" t="n"/>
       <c r="I33" s="16" t="n"/>
+      <c r="J33" s="16" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="16" t="n"/>
@@ -2771,6 +2817,7 @@
       <c r="G34" s="16" t="n"/>
       <c r="H34" s="16" t="n"/>
       <c r="I34" s="16" t="n"/>
+      <c r="J34" s="16" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="16" t="n"/>
@@ -2782,6 +2829,7 @@
       <c r="G35" s="16" t="n"/>
       <c r="H35" s="16" t="n"/>
       <c r="I35" s="16" t="n"/>
+      <c r="J35" s="16" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="16" t="n"/>
@@ -2793,6 +2841,7 @@
       <c r="G36" s="16" t="n"/>
       <c r="H36" s="16" t="n"/>
       <c r="I36" s="16" t="n"/>
+      <c r="J36" s="16" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="16" t="n"/>
@@ -2804,6 +2853,7 @@
       <c r="G37" s="16" t="n"/>
       <c r="H37" s="16" t="n"/>
       <c r="I37" s="16" t="n"/>
+      <c r="J37" s="16" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="16" t="n"/>
@@ -2815,6 +2865,7 @@
       <c r="G38" s="16" t="n"/>
       <c r="H38" s="16" t="n"/>
       <c r="I38" s="16" t="n"/>
+      <c r="J38" s="16" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="16" t="n"/>
@@ -2826,6 +2877,7 @@
       <c r="G39" s="16" t="n"/>
       <c r="H39" s="16" t="n"/>
       <c r="I39" s="16" t="n"/>
+      <c r="J39" s="16" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="16" t="n"/>
@@ -2837,6 +2889,7 @@
       <c r="G40" s="16" t="n"/>
       <c r="H40" s="16" t="n"/>
       <c r="I40" s="16" t="n"/>
+      <c r="J40" s="16" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="16" t="n"/>
@@ -2848,6 +2901,7 @@
       <c r="G41" s="16" t="n"/>
       <c r="H41" s="16" t="n"/>
       <c r="I41" s="16" t="n"/>
+      <c r="J41" s="16" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="16" t="n"/>
@@ -2859,6 +2913,7 @@
       <c r="G42" s="16" t="n"/>
       <c r="H42" s="16" t="n"/>
       <c r="I42" s="16" t="n"/>
+      <c r="J42" s="16" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="16" t="n"/>
@@ -2870,6 +2925,7 @@
       <c r="G43" s="16" t="n"/>
       <c r="H43" s="16" t="n"/>
       <c r="I43" s="16" t="n"/>
+      <c r="J43" s="16" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="16" t="n"/>
@@ -2881,6 +2937,7 @@
       <c r="G44" s="16" t="n"/>
       <c r="H44" s="16" t="n"/>
       <c r="I44" s="16" t="n"/>
+      <c r="J44" s="16" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="16" t="n"/>
@@ -2892,6 +2949,7 @@
       <c r="G45" s="16" t="n"/>
       <c r="H45" s="16" t="n"/>
       <c r="I45" s="16" t="n"/>
+      <c r="J45" s="16" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="16" t="n"/>
@@ -2903,6 +2961,7 @@
       <c r="G46" s="16" t="n"/>
       <c r="H46" s="16" t="n"/>
       <c r="I46" s="16" t="n"/>
+      <c r="J46" s="16" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="16" t="n"/>
@@ -2914,6 +2973,7 @@
       <c r="G47" s="16" t="n"/>
       <c r="H47" s="16" t="n"/>
       <c r="I47" s="16" t="n"/>
+      <c r="J47" s="16" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="16" t="n"/>
@@ -2925,6 +2985,7 @@
       <c r="G48" s="16" t="n"/>
       <c r="H48" s="16" t="n"/>
       <c r="I48" s="16" t="n"/>
+      <c r="J48" s="16" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="16" t="n"/>
@@ -2936,6 +2997,7 @@
       <c r="G49" s="16" t="n"/>
       <c r="H49" s="16" t="n"/>
       <c r="I49" s="16" t="n"/>
+      <c r="J49" s="16" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="16" t="n"/>
@@ -2947,6 +3009,7 @@
       <c r="G50" s="16" t="n"/>
       <c r="H50" s="16" t="n"/>
       <c r="I50" s="16" t="n"/>
+      <c r="J50" s="16" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="16" t="n"/>
@@ -2958,6 +3021,7 @@
       <c r="G51" s="16" t="n"/>
       <c r="H51" s="16" t="n"/>
       <c r="I51" s="16" t="n"/>
+      <c r="J51" s="16" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="16" t="n"/>
@@ -2969,6 +3033,7 @@
       <c r="G52" s="16" t="n"/>
       <c r="H52" s="16" t="n"/>
       <c r="I52" s="16" t="n"/>
+      <c r="J52" s="16" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="16" t="n"/>
@@ -2980,6 +3045,7 @@
       <c r="G53" s="16" t="n"/>
       <c r="H53" s="16" t="n"/>
       <c r="I53" s="16" t="n"/>
+      <c r="J53" s="16" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="16" t="n"/>
@@ -2991,6 +3057,7 @@
       <c r="G54" s="16" t="n"/>
       <c r="H54" s="16" t="n"/>
       <c r="I54" s="16" t="n"/>
+      <c r="J54" s="16" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="16" t="n"/>
@@ -3002,6 +3069,7 @@
       <c r="G55" s="16" t="n"/>
       <c r="H55" s="16" t="n"/>
       <c r="I55" s="16" t="n"/>
+      <c r="J55" s="16" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="16" t="n"/>
@@ -3013,6 +3081,7 @@
       <c r="G56" s="16" t="n"/>
       <c r="H56" s="16" t="n"/>
       <c r="I56" s="16" t="n"/>
+      <c r="J56" s="16" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="16" t="n"/>
@@ -3024,6 +3093,7 @@
       <c r="G57" s="16" t="n"/>
       <c r="H57" s="16" t="n"/>
       <c r="I57" s="16" t="n"/>
+      <c r="J57" s="16" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="16" t="n"/>
@@ -3035,6 +3105,7 @@
       <c r="G58" s="16" t="n"/>
       <c r="H58" s="16" t="n"/>
       <c r="I58" s="16" t="n"/>
+      <c r="J58" s="16" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="16" t="n"/>
@@ -3046,6 +3117,7 @@
       <c r="G59" s="16" t="n"/>
       <c r="H59" s="16" t="n"/>
       <c r="I59" s="16" t="n"/>
+      <c r="J59" s="16" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="16" t="n"/>
@@ -3057,6 +3129,7 @@
       <c r="G60" s="16" t="n"/>
       <c r="H60" s="16" t="n"/>
       <c r="I60" s="16" t="n"/>
+      <c r="J60" s="16" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="16" t="n"/>
@@ -3068,6 +3141,7 @@
       <c r="G61" s="16" t="n"/>
       <c r="H61" s="16" t="n"/>
       <c r="I61" s="16" t="n"/>
+      <c r="J61" s="16" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="16" t="n"/>
@@ -3079,6 +3153,7 @@
       <c r="G62" s="16" t="n"/>
       <c r="H62" s="16" t="n"/>
       <c r="I62" s="16" t="n"/>
+      <c r="J62" s="16" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="16" t="n"/>
@@ -3090,6 +3165,7 @@
       <c r="G63" s="16" t="n"/>
       <c r="H63" s="16" t="n"/>
       <c r="I63" s="16" t="n"/>
+      <c r="J63" s="16" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="16" t="n"/>
@@ -3101,9 +3177,10 @@
       <c r="G64" s="16" t="n"/>
       <c r="H64" s="16" t="n"/>
       <c r="I64" s="16" t="n"/>
+      <c r="J64" s="16" t="n"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="A3:A64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$P$2:$P$4</formula1>
     </dataValidation>
@@ -3114,6 +3191,9 @@
       <formula1>=Listes!$Q$2:$Q$4</formula1>
     </dataValidation>
     <dataValidation sqref="H3:H64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="I3:I64" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$N$2:$N$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1469,13 +1469,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="33" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$M$2:$M$4</formula1>
     </dataValidation>
     <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
       <formula1>=Listes!$N$2:$N$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"confirmed,needs_confirmation"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -4046,7 +4046,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4500,6 +4500,20 @@
       <c r="D25" s="18" t="inlineStr">
         <is>
           <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
         </is>
       </c>
     </row>
@@ -8686,7 +8700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O404"/>
+  <dimension ref="A1:Q404"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8704,6 +8718,8 @@
     <col width="13" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -8782,6 +8798,16 @@
           <t>controle  (auto)</t>
         </is>
       </c>
+      <c r="P1" s="14" t="inlineStr">
+        <is>
+          <t>partage_bas</t>
+        </is>
+      </c>
+      <c r="Q1" s="14" t="inlineStr">
+        <is>
+          <t>seuil_partage</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -8857,6 +8883,16 @@
       <c r="O2" s="25" t="inlineStr">
         <is>
           <t>ok, ou plan introuvable.</t>
+        </is>
+      </c>
+      <c r="P2" s="25" t="inlineStr">
+        <is>
+          <t>Partage par palier : le taux SOUS le seuil (50 %). Vide si un seul taux. Le taux au-dessus va dans « partage ».</t>
+        </is>
+      </c>
+      <c r="Q2" s="25" t="inlineStr">
+        <is>
+          <t>Montant d'une demande de retrait a partir duquel « partage » s'applique. En devise. Avec partage_bas.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -3670,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:Q7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4016,6 +4016,11 @@
           <t>needs_confirmation</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>certification</t>
+        </is>
+      </c>
       <c r="G5" s="11" t="inlineStr">
         <is>
           <t>crypto</t>
@@ -4034,6 +4039,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4767,12 +4773,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4791,6 +4798,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -4806,6 +4818,11 @@
       <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Pourquoi, d'ou vient le nom. Non affiche.</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Icone officielle, prise sur le site de l'editeur (https). Vide : pastille a l'initiale.</t>
         </is>
       </c>
     </row>
@@ -5488,7 +5505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L153"/>
+  <dimension ref="A1:M153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5503,6 +5520,7 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5566,6 +5584,11 @@
           <t>controle  (auto)</t>
         </is>
       </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>lien_plan</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -5626,6 +5649,11 @@
       <c r="L2" s="25" t="inlineStr">
         <is>
           <t>ok, ou ce qui manque.</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>Slug du plan dans prop_firm_challenges (voir DIAGNOSTIC-liens-plans). Les boutons ouvrent alors son lien profond : paiement de CE plan, code applique. Vide : lien general de la firme.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -3670,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4039,7 +4039,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4052,7 +4051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4520,6 +4519,20 @@
       <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
         </is>
       </c>
     </row>
@@ -17047,7 +17060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -17056,6 +17069,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17089,6 +17103,11 @@
           <t>programmes</t>
         </is>
       </c>
+      <c r="G1" s="14" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -17119,6 +17138,11 @@
       <c r="F2" s="25" t="inlineStr">
         <is>
           <t>Slugs concernes, separes par des virgules. Vide : tous les programmes.</t>
+        </is>
+      </c>
+      <c r="G2" s="25" t="inlineStr">
+        <is>
+          <t>Icone officielle de l'option, prise sur le site de l'editeur (https). Vide : logo de la plateforme du meme nom, sinon initiale.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -5518,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M153"/>
+  <dimension ref="A1:N153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5534,6 +5534,7 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -5602,6 +5603,11 @@
           <t>lien_plan</t>
         </is>
       </c>
+      <c r="N1" s="14" t="inlineStr">
+        <is>
+          <t>devise_compte</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -5667,6 +5673,11 @@
       <c r="M2" s="25" t="inlineStr">
         <is>
           <t>Slug du plan dans prop_firm_challenges (voir DIAGNOSTIC-liens-plans). Les boutons ouvrent alors son lien profond : paiement de CE plan, code applique. Vide : lien general de la firme.</t>
+        </is>
+      </c>
+      <c r="N2" s="25" t="inlineStr">
+        <is>
+          <t>Devise du SOLDE du compte : la taille, l'objectif et les limites. Vide : la devise du prix. A remplir quand la firme facture dans une monnaie et libelle les comptes dans une autre.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -2293,7 +2293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:K64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2359,6 +2359,11 @@
           <t>source_url</t>
         </is>
       </c>
+      <c r="K1" s="14" t="inlineStr">
+        <is>
+          <t>variantes</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -2409,6 +2414,11 @@
       <c r="J2" s="25" t="inlineStr">
         <is>
           <t>Page officielle. Non affichee.</t>
+        </is>
+      </c>
+      <c r="K2" s="25" t="inlineStr">
+        <is>
+          <t>Variantes concernees (Day Trade, Swing, NEW...), separees par des virgules. Vide : toutes.</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q6"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3971,12 +3981,12 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>retired</t>
+          <t>limited_offer</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
         <is>
-          <t>funded</t>
+          <t>evaluation_3</t>
         </is>
       </c>
       <c r="K4" s="11" t="inlineStr">
@@ -4006,7 +4016,7 @@
       </c>
       <c r="Q4" s="11" t="inlineStr">
         <is>
-          <t>funded</t>
+          <t>evaluation_3</t>
         </is>
       </c>
     </row>
@@ -4026,9 +4036,24 @@
           <t>crypto</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>retired</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>funded</t>
+        </is>
+      </c>
       <c r="K5" s="11" t="inlineStr">
         <is>
           <t>Static</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>funded</t>
         </is>
       </c>
     </row>
@@ -4039,6 +4064,9 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
+    <row r="8"/>
+    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4987,7 +5015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5059,6 +5087,16 @@
           <t>nb_plans  (auto)</t>
         </is>
       </c>
+      <c r="L1" s="14" t="inlineStr">
+        <is>
+          <t>offre_fin</t>
+        </is>
+      </c>
+      <c r="M1" s="14" t="inlineStr">
+        <is>
+          <t>offre_fin_statut</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="25" t="inlineStr">
@@ -5114,6 +5152,16 @@
       <c r="K2" s="25" t="inlineStr">
         <is>
           <t>Plans rattaches.</t>
+        </is>
+      </c>
+      <c r="L2" s="25" t="inlineStr">
+        <is>
+          <t>Campagne a duree limitee : sa date de fin. Vide si le programme est permanent.</t>
+        </is>
+      </c>
+      <c r="M2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed si la date est publiee. Sinon not_published, needs_confirmation ou source_conflict.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1484,6 +1484,18 @@
       <c r="D9" s="18" t="inlineStr">
         <is>
           <t>Seule une offre confirmed s'affiche : remise, code, Copy code et Claim deal. Vide ou needs_confirmation : la carte garde le plan, le prix public et Continue to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>accroche</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="inlineStr">
+        <is>
+          <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S9"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4064,9 +4076,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8"/>
-    <row r="9"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1496,6 +1496,30 @@
       <c r="D10" s="15" t="inlineStr">
         <is>
           <t>Une phrase courte pour le bandeau de campagne du site : ce que l'offre donne, en plus du pourcentage. Vide : le bandeau n'affiche que la remise.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>remise_campagne</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>Taux d'une campagne a duree limitee, en %. Il remplace « remise » jusqu'a « campagne_fin », puis la fiche revient a « remise ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>campagne_fin</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -1314,7 +1314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1520,6 +1520,18 @@
       <c r="D12" s="15" t="inlineStr">
         <is>
           <t>Fin de la campagne, date et heure ISO. Passee, le taux de campagne et l'accroche disparaissent, l'offre permanente reste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>bonus</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots pour ce que l'offre donne en plus du pourcentage (« +1 free reset »). Affiche en pastille sur la fiche et sur la carte /compare. Suit la campagne : il disparait avec elle.</t>
         </is>
       </c>
     </row>

--- a/MODELE-propfirm.xlsx
+++ b/MODELE-propfirm.xlsx
@@ -17,15 +17,16 @@
     <sheet name="Phases" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="OptionsAchat" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Offre" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Conditions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Parcours" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Formation" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="ComptesApresReussite" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Couts" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Regles" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="Verdict" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="FAQ" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="Listes" sheetId="19" state="hidden" r:id="rId19"/>
+    <sheet name="Campagnes" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Conditions" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Parcours" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ComptesApresReussite" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Couts" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Regles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Verdict" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="FAQ" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Listes" sheetId="20" state="hidden" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1555,6 +1556,92 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>debut</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>fin</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>detail</t>
+        </is>
+      </c>
+      <c r="E1" s="14" t="inlineStr">
+        <is>
+          <t>remise</t>
+        </is>
+      </c>
+      <c r="F1" s="14" t="inlineStr">
+        <is>
+          <t>statut</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO d'ouverture. Avant elle, la campagne n'existe nulle part.</t>
+        </is>
+      </c>
+      <c r="B2" s="25" t="inlineStr">
+        <is>
+          <t>Date et heure ISO de fermeture. Passee, la campagne disparait d'elle-meme.</t>
+        </is>
+      </c>
+      <c r="C2" s="25" t="inlineStr">
+        <is>
+          <t>Deux ou trois mots, pour la pastille : « Day 4 · -60% TCP25 ».</t>
+        </is>
+      </c>
+      <c r="D2" s="25" t="inlineStr">
+        <is>
+          <t>Une phrase : ce que l'offre donne, telle qu'elle s'affiche.</t>
+        </is>
+      </c>
+      <c r="E2" s="25" t="inlineStr">
+        <is>
+          <t>Taux pendant la fenetre, en %. Vide : le taux habituel de l'offre ne change pas.</t>
+        </is>
+      </c>
+      <c r="F2" s="25" t="inlineStr">
+        <is>
+          <t>confirmed pour s'afficher. Toute autre valeur la garde en reserve.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="004B5563"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1650,7 +1737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1853,7 +1940,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -1963,7 +2050,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2152,7 +2239,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -2334,7 +2421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="004B5563"/>
@@ -3281,7 +3368,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -3536,7 +3623,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="006B7280"/>
@@ -3721,7 +3808,513 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F2937"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="14" t="inlineStr">
+        <is>
+          <t>Champ</t>
+        </is>
+      </c>
+      <c r="B1" s="14" t="inlineStr">
+        <is>
+          <t>Valeur a remplir</t>
+        </is>
+      </c>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>Exemple — FuturesElite, 7 sept. 2026</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>Ou ca s'affiche dans le HTML · si vide</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="44" customHeight="1">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>slug</t>
+        </is>
+      </c>
+      <c r="B2" s="16" t="n"/>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>futureselite</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="inlineStr">
+        <is>
+          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="44" customHeight="1">
+      <c r="A3" s="15" t="inlineStr">
+        <is>
+          <t>nom</t>
+        </is>
+      </c>
+      <c r="B3" s="16" t="n"/>
+      <c r="C3" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>logo_url</t>
+        </is>
+      </c>
+      <c r="B4" s="16" t="n"/>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44" customHeight="1">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_score</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="n"/>
+      <c r="C5" s="20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D5" s="18" t="inlineStr">
+        <is>
+          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_review_count</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="n"/>
+      <c r="C6" s="22" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D6" s="18" t="inlineStr">
+        <is>
+          <t>Nombre d'avis sous la note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="44" customHeight="1">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>trustpilot_url</t>
+        </is>
+      </c>
+      <c r="B7" s="16" t="n"/>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>https://www.trustpilot.com/review/exemple.com</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>marches</t>
+        </is>
+      </c>
+      <c r="B8" s="16" t="n"/>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>futures</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="inlineStr">
+        <is>
+          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="44" customHeight="1">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>titre</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="n"/>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>Four routes to a funded futures account</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="44" customHeight="1">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>resume</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="44" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>presentation</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="inlineStr">
+        <is>
+          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="44" customHeight="1">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>annee_creation</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="24" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>« Founded ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="44" customHeight="1">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>pays</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="n"/>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>« Country ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="44" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>ceo_fondateur</t>
+        </is>
+      </c>
+      <c r="B15" s="16" t="n"/>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Christian Habibi</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>« CEO / Founder ». Vide : « — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="44" customHeight="1">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>actifs</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="n"/>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs</t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="n"/>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>(vide — non confirmees)</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>categories_actifs_statut</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="n"/>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>needs_confirmation</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="15" t="inlineStr">
+        <is>
+          <t>plateformes</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="n"/>
+      <c r="C19" s="17" t="inlineStr">
+        <is>
+          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="44" customHeight="1">
+      <c r="A20" s="15" t="inlineStr">
+        <is>
+          <t>moyens_paiement</t>
+        </is>
+      </c>
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>Credit/Debit Card, Crypto</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="inlineStr">
+        <is>
+          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="44" customHeight="1">
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>methodes_retrait</t>
+        </is>
+      </c>
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Crypto, Riseworks</t>
+        </is>
+      </c>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="44" customHeight="1">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>prestataire_retrait</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Rise</t>
+        </is>
+      </c>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="44" customHeight="1">
+      <c r="A23" s="15" t="inlineStr">
+        <is>
+          <t>levier</t>
+        </is>
+      </c>
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>N/A (futures contracts)</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="44" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>levier_statut</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="44" customHeight="1">
+      <c r="A25" s="15" t="inlineStr">
+        <is>
+          <t>styles_trading</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>(vide — absent du releve)</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>meta_description</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
+        <is>
+          <t>flux_donnees</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
+      <formula1>=Listes!$A$2:$A$6</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009CA3AF"/>
@@ -4114,512 +4707,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="001F2937"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
-    <col width="44" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="14" t="inlineStr">
-        <is>
-          <t>Champ</t>
-        </is>
-      </c>
-      <c r="B1" s="14" t="inlineStr">
-        <is>
-          <t>Valeur a remplir</t>
-        </is>
-      </c>
-      <c r="C1" s="14" t="inlineStr">
-        <is>
-          <t>Exemple — FuturesElite, 7 sept. 2026</t>
-        </is>
-      </c>
-      <c r="D1" s="14" t="inlineStr">
-        <is>
-          <t>Ou ca s'affiche dans le HTML · si vide</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="44" customHeight="1">
-      <c r="A2" s="15" t="inlineStr">
-        <is>
-          <t>slug</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n"/>
-      <c r="C2" s="17" t="inlineStr">
-        <is>
-          <t>futureselite</t>
-        </is>
-      </c>
-      <c r="D2" s="18" t="inlineStr">
-        <is>
-          <t>N'est pas affiche : sert a l'adresse de la page et au lien sortant. Minuscules, sans espace. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="44" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>nom</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite</t>
-        </is>
-      </c>
-      <c r="D3" s="18" t="inlineStr">
-        <is>
-          <t>Le titre de la carte d'identite, « Continue to [Firm] », le verdict et la FAQ. Obligatoire.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44" customHeight="1">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>logo_url</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>https://www.google.com/s2/favicons?domain=futureselite.com&amp;sz=128</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>Le logo, en tuile blanche. Il n'est pas cliquable : les sorties passent par Claim deal et Continue to. Vide : initiale du nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="44" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_score</t>
-        </is>
-      </c>
-      <c r="B5" s="19" t="n"/>
-      <c r="C5" s="20" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>Hero, angle haut droit : note sur 5. Vide : le bloc Trustpilot n'apparait pas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44" customHeight="1">
-      <c r="A6" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_review_count</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="n"/>
-      <c r="C6" s="22" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>Nombre d'avis sous la note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="44" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
-        <is>
-          <t>trustpilot_url</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>https://www.trustpilot.com/review/exemple.com</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>Page Trustpilot de la firme : le badge y renvoie. Vide : badge non cliquable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="44" customHeight="1">
-      <c r="A8" s="15" t="inlineStr">
-        <is>
-          <t>marches</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>futures</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>« Firm type » (deduit d'ici) et le choix du marche dans le configurateur. futures, cfd — separes par une virgule si plusieurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="44" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>titre</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="n"/>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Four routes to a funded futures account</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : le H1, une proposition de valeur. Vide : le nom de la firme sert de H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Compare Elite, Nitro, Prime and Instant to choose between a traditional evaluation, a faster route or funding from purchase.</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : 2 a 3 lignes sous le H1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="44" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>resume</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Elite and Prime are evaluation routes with a one-time fee and no deadline to pass. Nitro and Instant shorten or remove the evaluation entirely, Instant funding you from purchase with no objective to reach.</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement (retour arriere) : 1 a 2 phrases sous le nom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="44" customHeight="1">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>presentation</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>FuturesElite sells simulated futures accounts across four programs. Elite and Prime are evaluation routes with a one-time fee and no deadline to pass.</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="inlineStr">
-        <is>
-          <t>Section « About [Firm] » : texte developpe, paragraphes separes par une ligne vide (Alt+Entree deux fois).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>annee_creation</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="24" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>« Founded ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="44" customHeight="1">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>pays</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>« Country ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="44" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>ceo_fondateur</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Christian Habibi</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>« CEO / Founder ». Vide : « — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="44" customHeight="1">
-      <c r="A16" s="15" t="inlineStr">
-        <is>
-          <t>actifs</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Futures, Forex, Metals, Indices, Energy, Crypto, Bonds, Agricultural Products</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement : une etiquette par actif, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="44" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>(vide — non confirmees)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page, « Tradable assets » : categories precises (Index futures, Currency futures…), seulement si confirmees par la firme.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="44" customHeight="1">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>categories_actifs_statut</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>needs_confirmation</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>confirmed si la liste est confirmee. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="44" customHeight="1">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>plateformes</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Tradovate, NinjaTrader, Quantower, ATAS, WealthCharts, DeepChart, Volumetrica, DeepCharts</t>
-        </is>
-      </c>
-      <c r="D19" s="18" t="inlineStr">
-        <is>
-          <t>Ancienne page seulement. La nouvelle lit l'onglet Plateformes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="44" customHeight="1">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>moyens_paiement</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Credit/Debit Card, Crypto</t>
-        </is>
-      </c>
-      <c r="D20" s="18" t="inlineStr">
-        <is>
-          <t>« Purchase methods » : moyens de paiement A L'ACHAT, separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="44" customHeight="1">
-      <c r="A21" s="15" t="inlineStr">
-        <is>
-          <t>methodes_retrait</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Crypto, Riseworks</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : methodes de RETRAIT, separees par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="44" customHeight="1">
-      <c r="A22" s="15" t="inlineStr">
-        <is>
-          <t>prestataire_retrait</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Rise</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>Carte PAYOUTS : le prestataire qui paie les retraits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="44" customHeight="1">
-      <c r="A23" s="15" t="inlineStr">
-        <is>
-          <t>levier</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>N/A (futures contracts)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : « Leverage 1:X ». Vide : « Leverage — ».</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="44" customHeight="1">
-      <c r="A24" s="15" t="inlineStr">
-        <is>
-          <t>levier_statut</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>Nouvelle page : confirmed si levier est rempli. Ou un statut : not_published (la firme ne le publie pas), not_applicable, needs_confirmation, source_conflict. Vide : la ligne disparait.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="44" customHeight="1">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>styles_trading</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>(vide — absent du releve)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>« Trading profile » : styles autorises (Swing…), separes par des virgules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
-        <is>
-          <t>meta_description</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>Meta description de la page (Google). Vide : calculee depuis la presentation. 160 caracteres au plus.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="inlineStr">
-        <is>
-          <t>flux_donnees</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>Carte « Data feeds » : flux de donnees proposes, separes par des virgules. Affichage seulement.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="B18" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-    <dataValidation sqref="B24" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisis une valeur dans la liste deroulante." type="list">
-      <formula1>=Listes!$A$2:$A$6</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
